--- a/aula1803projeotimalg.xlsx
+++ b/aula1803projeotimalg.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Windows\Users\henri\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Windows\Users\henri\Desktop\pucrs\5 sem\proj. e otim. de alg\4-divisao-e-conquista-exercicio-de-aprofundamento-lasanha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE3619F-DA22-4E45-B754-F76B93A6C80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568FF2C1-B84D-4DE3-A7C2-FC2C7FD48D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="264" windowWidth="21840" windowHeight="12312" xr2:uid="{8A858C71-B9C0-469D-A2E7-D54C61CDC35C}"/>
+    <workbookView xWindow="1092" yWindow="-108" windowWidth="22056" windowHeight="13176" xr2:uid="{8A858C71-B9C0-469D-A2E7-D54C61CDC35C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>MergeSort</t>
   </si>
@@ -77,6 +77,21 @@
   <si>
     <t>Iterações: 1365
 Tempo: 0</t>
+  </si>
+  <si>
+    <t>multiply2</t>
+  </si>
+  <si>
+    <t>Iterações: 5
+Tempo: 0</t>
+  </si>
+  <si>
+    <t>Iterações: 17
+Tempo: 0</t>
+  </si>
+  <si>
+    <t>Iterações: 33
+Tempo: 1</t>
   </si>
 </sst>
 </file>
@@ -502,6 +517,18 @@
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">

--- a/aula1803projeotimalg.xlsx
+++ b/aula1803projeotimalg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Windows\Users\henri\Desktop\pucrs\5 sem\proj. e otim. de alg\4-divisao-e-conquista-exercicio-de-aprofundamento-lasanha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568FF2C1-B84D-4DE3-A7C2-FC2C7FD48D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D94F281-CDE6-4DC5-932F-366D44238801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1092" yWindow="-108" windowWidth="22056" windowHeight="13176" xr2:uid="{8A858C71-B9C0-469D-A2E7-D54C61CDC35C}"/>
+    <workbookView xWindow="1884" yWindow="468" windowWidth="21840" windowHeight="12312" xr2:uid="{8A858C71-B9C0-469D-A2E7-D54C61CDC35C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,23 +75,23 @@
 Tempo: 0</t>
   </si>
   <si>
-    <t>Iterações: 1365
-Tempo: 0</t>
-  </si>
-  <si>
     <t>multiply2</t>
   </si>
   <si>
-    <t>Iterações: 5
-Tempo: 0</t>
-  </si>
-  <si>
-    <t>Iterações: 17
-Tempo: 0</t>
-  </si>
-  <si>
-    <t>Iterações: 33
-Tempo: 1</t>
+    <t>Iterações: 5461
+Tempo: 0</t>
+  </si>
+  <si>
+    <t>Iterações: 10
+Tempo: 0</t>
+  </si>
+  <si>
+    <t>Iterações: 42
+Tempo: 0</t>
+  </si>
+  <si>
+    <t>Iterações: 129
+Tempo: 0</t>
   </si>
 </sst>
 </file>
@@ -446,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C23DE619-DDA4-4614-B39D-36BFC89884CD}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
@@ -458,7 +458,7 @@
     <col min="9" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>32</v>
       </c>
@@ -468,17 +468,8 @@
       <c r="D1">
         <v>1048576</v>
       </c>
-      <c r="G1">
-        <v>4</v>
-      </c>
-      <c r="H1">
-        <v>16</v>
-      </c>
-      <c r="I1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -491,20 +482,8 @@
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -517,20 +496,8 @@
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -542,6 +509,45 @@
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
